--- a/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/Month to Date (Actual)_Visits.xlsx
@@ -31,13 +31,13 @@
     <t>Location</t>
   </si>
   <si>
+    <t>Snowbowl Comp Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Passes</t>
   </si>
   <si>
     <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
     <t>Snowbowl Tickets</t>
@@ -431,10 +431,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C2" s="2">
-        <v>14</v>
+        <v>488</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,13 +445,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C3" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C4" s="2">
-        <v>13</v>
+        <v>356</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C6" s="2">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,13 +501,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>46028</v>
+        <v>46024</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,13 +515,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C8" s="2">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46023</v>
+        <v>46026</v>
       </c>
       <c r="C10" s="2">
-        <v>511</v>
+        <v>539</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>7</v>
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="C12" s="2">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,7 +588,7 @@
         <v>46023</v>
       </c>
       <c r="C13" s="2">
-        <v>374</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
@@ -599,10 +599,10 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C14" s="2">
-        <v>14</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>5</v>
@@ -613,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>46024</v>
+        <v>46026</v>
       </c>
       <c r="C15" s="2">
-        <v>34</v>
+        <v>268</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C16" s="2">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,10 +641,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C17" s="2">
-        <v>539</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>6</v>
@@ -655,13 +655,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>46027</v>
+        <v>46023</v>
       </c>
       <c r="C18" s="2">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C19" s="2">
-        <v>652</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C20" s="2">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C21" s="2">
-        <v>1917</v>
+        <v>378</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +711,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>46028</v>
+        <v>46023</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C24" s="2">
-        <v>1546</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -753,13 +753,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C25" s="2">
-        <v>631</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>551</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,13 +781,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C27" s="2">
-        <v>368</v>
+        <v>11</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C28" s="2">
-        <v>1</v>
+        <v>658</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>46023</v>
+        <v>46028</v>
       </c>
       <c r="C29" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,13 +823,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C30" s="2">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>46025</v>
+        <v>46023</v>
       </c>
       <c r="C31" s="2">
         <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,10 +851,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C32" s="2">
-        <v>551</v>
+        <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -865,13 +865,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C33" s="2">
-        <v>11</v>
+        <v>987</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>46026</v>
+        <v>46024</v>
       </c>
       <c r="C34" s="2">
-        <v>658</v>
+        <v>1622</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,13 +893,13 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,10 +907,10 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>46028</v>
+        <v>46025</v>
       </c>
       <c r="C36" s="2">
-        <v>241</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>6</v>
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>46023</v>
+        <v>46025</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>452</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>46023</v>
+        <v>46027</v>
       </c>
       <c r="C38" s="2">
-        <v>1420</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,13 +949,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C39" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,10 +963,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>6</v>
@@ -977,13 +977,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>46025</v>
+        <v>46027</v>
       </c>
       <c r="C41" s="2">
-        <v>52</v>
+        <v>1826</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,10 +991,10 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="C42" s="2">
-        <v>844</v>
+        <v>279</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1005,13 +1005,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>46026</v>
+        <v>46023</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>652</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C44" s="2">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>46026</v>
+        <v>46025</v>
       </c>
       <c r="C45" s="2">
-        <v>1451</v>
+        <v>1917</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>8</v>
@@ -1047,13 +1047,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>46027</v>
+        <v>46025</v>
       </c>
       <c r="C46" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,10 +1064,10 @@
         <v>46028</v>
       </c>
       <c r="C47" s="2">
-        <v>472</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>46023</v>
+        <v>46028</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>1546</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C50" s="2">
-        <v>987</v>
+        <v>1420</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,10 +1120,10 @@
         <v>46024</v>
       </c>
       <c r="C51" s="2">
-        <v>1622</v>
+        <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>46025</v>
+        <v>46024</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1148,10 @@
         <v>46025</v>
       </c>
       <c r="C53" s="2">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,10 +1162,10 @@
         <v>46025</v>
       </c>
       <c r="C54" s="2">
-        <v>566</v>
+        <v>844</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C55" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>46027</v>
+        <v>46026</v>
       </c>
       <c r="C57" s="2">
-        <v>550</v>
+        <v>1451</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>46027</v>
       </c>
       <c r="C58" s="2">
-        <v>1826</v>
+        <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>46028</v>
       </c>
       <c r="C59" s="2">
-        <v>280</v>
+        <v>472</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
